--- a/data/trans_bre/P45C_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,28</t>
+          <t>-1,23; 0,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,72</t>
+          <t>-1,19; 1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,25</t>
+          <t>-0,85; 1,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,28</t>
+          <t>-0,4; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 145,73</t>
+          <t>-48,79; 185,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 371,99</t>
+          <t>-60,56; 351,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 444,8</t>
+          <t>-31,45; 459,81</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,16</t>
+          <t>-1,05; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,16</t>
+          <t>-0,98; 1,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,51</t>
+          <t>-0,32; 1,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,4</t>
+          <t>-1,32; 1,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 145,34</t>
+          <t>-53,89; 129,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 150,28</t>
+          <t>-52,4; 151,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,14; 485,77</t>
+          <t>-39,96; 424,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 186,47</t>
+          <t>-52,52; 155,44</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,53</t>
+          <t>-2,13; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,38</t>
+          <t>-1,72; 0,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,87</t>
+          <t>-1,76; 0,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,24</t>
+          <t>-2,67; 1,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 96,97</t>
+          <t>-56,09; 90,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,72; 63,83</t>
+          <t>-81,45; 64,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,7; 110,97</t>
+          <t>-72,53; 101,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 96,64</t>
+          <t>-75,07; 101,68</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,37</t>
+          <t>-1,13; 1,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,45</t>
+          <t>0,41; 2,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,11</t>
+          <t>-0,36; 1,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; -0,26</t>
+          <t>-2,14; -0,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,65; 101,88</t>
+          <t>-42,42; 110,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 653,47</t>
+          <t>14,74; 696,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 430,46</t>
+          <t>-47,03; 383,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,59; -15,75</t>
+          <t>-85,68; -15,53</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,6</t>
+          <t>-0,67; 0,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,87</t>
+          <t>-0,3; 0,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,71</t>
+          <t>-0,29; 0,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,47</t>
+          <t>-0,94; 0,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 44,34</t>
+          <t>-33,1; 47,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 86,68</t>
+          <t>-21,59; 83,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 100,73</t>
+          <t>-26,87; 106,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 37,47</t>
+          <t>-44,58; 38,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,28</t>
+          <t>-1,09; 0,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,87</t>
+          <t>-1,29; 1,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,29</t>
+          <t>-0,91; 1,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,19</t>
+          <t>-0,41; 2,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 185,99</t>
+          <t>-51,95; 176,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,56; 351,28</t>
+          <t>-65,74; 327,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 459,81</t>
+          <t>-38,17; 435,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>-12,33%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,19</t>
+          <t>-0,99; 1,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,19</t>
+          <t>-1,05; 1,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,58</t>
+          <t>-0,43; 1,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,3</t>
+          <t>-1,5; 0,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 129,24</t>
+          <t>-50,53; 147,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 151,56</t>
+          <t>-53,81; 126,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 424,8</t>
+          <t>-46,92; 436,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 155,44</t>
+          <t>-56,13; 73,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,81%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,65</t>
+          <t>-2,22; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,39</t>
+          <t>-1,75; 0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,89</t>
+          <t>-1,61; 0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,26</t>
+          <t>-1,76; 1,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 90,84</t>
+          <t>-56,55; 89,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 64,08</t>
+          <t>-83,62; 83,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-72,53; 101,64</t>
+          <t>-67,55; 117,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 101,68</t>
+          <t>-52,17; 119,99</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-64,49%</t>
+          <t>-59,76%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,46</t>
+          <t>-1,28; 1,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,52</t>
+          <t>0,38; 2,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,02</t>
+          <t>-0,29; 1,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,14; -0,2</t>
+          <t>-1,93; -0,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 110,9</t>
+          <t>-45,38; 112,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,74; 696,3</t>
+          <t>6,84; 648,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 383,8</t>
+          <t>-52,44; 405,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,68; -15,53</t>
+          <t>-83,76; -6,11</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-11,78%</t>
+          <t>-9,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,65</t>
+          <t>-0,63; 0,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,88</t>
+          <t>-0,25; 0,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,72</t>
+          <t>-0,29; 0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,44</t>
+          <t>-0,8; 0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 47,06</t>
+          <t>-31,66; 48,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 83,81</t>
+          <t>-15,74; 84,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 106,1</t>
+          <t>-26,14; 101,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 38,0</t>
+          <t>-38,07; 35,07</t>
         </is>
       </c>
     </row>
